--- a/output/pdf_financials_xlsx/SOO.P.xlsx
+++ b/output/pdf_financials_xlsx/SOO.P.xlsx
@@ -2492,19 +2492,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.06012</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.06012</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.06012</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.06012</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.06012</v>
       </c>
     </row>
     <row r="93">
@@ -3765,7 +3765,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4181,7 +4185,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -4566,7 +4574,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.06012</v>
       </c>

--- a/output/pdf_financials_xlsx/SOO.P.xlsx
+++ b/output/pdf_financials_xlsx/SOO.P.xlsx
@@ -1180,19 +1180,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.007138</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.00066</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.7e-05</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.004146</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.057857</v>
       </c>
     </row>
     <row r="35">
@@ -1224,19 +1224,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.007138</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.00066</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.7e-05</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.004146</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.057857</v>
       </c>
     </row>
     <row r="37">
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.007165</v>
+        <v>2.7e-05</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.00066</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.7e-05</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/SOO.P.xlsx
+++ b/output/pdf_financials_xlsx/SOO.P.xlsx
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.047603</v>
+        <v>0.04767</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.032947</v>
+        <v>0.033007</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.037466</v>
+        <v>0.037536</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.032204</v>
+        <v>0.032264</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.012852</v>
+        <v>0.01291</v>
       </c>
     </row>
     <row r="8">
@@ -785,7 +785,7 @@
         <v>0.01</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003958</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.000298</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.008787</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0</v>
@@ -2785,13 +2785,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.008817</v>
+        <v>0.004859</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.043054</v>
+        <v>0.043352</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.061678</v>
+        <v>0.070465</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.029923</v>
@@ -4953,7 +4953,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -5293,7 +5297,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -5332,7 +5340,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>-0.003958</v>
       </c>
@@ -6033,7 +6045,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -6447,7 +6463,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>6.7e-05</v>
       </c>
@@ -6954,7 +6974,11 @@
           <t>Deferred income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -7198,7 +7222,11 @@
           <t>Deferred income tax recovery (expense) (Note 10)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
